--- a/artfynd/A 43788-2023 artfynd.xlsx
+++ b/artfynd/A 43788-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43788-2023 artfynd.xlsx
+++ b/artfynd/A 43788-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112784949</v>
+        <v>112784864</v>
       </c>
       <c r="B2" t="n">
-        <v>91185</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570717</v>
+        <v>570492</v>
       </c>
       <c r="R2" t="n">
-        <v>6397588</v>
+        <v>6397565</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112784930</v>
+        <v>112784881</v>
       </c>
       <c r="B3" t="n">
-        <v>91185</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570532</v>
+        <v>570492</v>
       </c>
       <c r="R3" t="n">
-        <v>6397549</v>
+        <v>6397565</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,6 +890,442 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112784930</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 43788, Hultserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>570532</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6397549</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112784949</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 43788, Hultserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>570717</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6397588</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112784982</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tätsjön, Hultserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>570630</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6397424</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97671785</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rumhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>570495</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6397588</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-04-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-04-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>JSN0173 (Calluna AB) Fågelinventering.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Spillning på berghäll</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jens Wikström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
